--- a/dados/ambev-spot-t1.xlsx
+++ b/dados/ambev-spot-t1.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEMARCO.TALLISON\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupodemarco-my.sharepoint.com/personal/tallison_jesus_demarco_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{699BCB89-F28B-4BA2-AD4B-EC07809E0432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{8D22D165-2D9C-4516-9ADF-B65891E08959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A648F1-ECFC-4969-8137-B3EC14F4F32A}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$D$496</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="499">
   <si>
     <t>Identificador</t>
   </si>
@@ -34,21 +37,12 @@
     <t>Motivo</t>
   </si>
   <si>
-    <t>Frente</t>
-  </si>
-  <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>Traseira</t>
-  </si>
-  <si>
     <t>- Lateral</t>
   </si>
   <si>
-    <t>- Frente</t>
-  </si>
-  <si>
     <t>ENN8E45</t>
   </si>
   <si>
@@ -1288,15 +1282,6 @@
     <t>- lateral</t>
   </si>
   <si>
-    <t>- FRENTE</t>
-  </si>
-  <si>
-    <t>Traseira.</t>
-  </si>
-  <si>
-    <t>Traseira e Lateral</t>
-  </si>
-  <si>
     <t>- LATERAL</t>
   </si>
   <si>
@@ -1310,6 +1295,231 @@
   </si>
   <si>
     <t>Bug pendente Frente e Lateral</t>
+  </si>
+  <si>
+    <t>RKZ6I31</t>
+  </si>
+  <si>
+    <t>FIX2B24</t>
+  </si>
+  <si>
+    <t>RYV0H63</t>
+  </si>
+  <si>
+    <t>RYV0I03</t>
+  </si>
+  <si>
+    <t>IWX0D94</t>
+  </si>
+  <si>
+    <t>IGV7919</t>
+  </si>
+  <si>
+    <t>SKN4G32</t>
+  </si>
+  <si>
+    <t>RLB2E24</t>
+  </si>
+  <si>
+    <t>RYY8E41</t>
+  </si>
+  <si>
+    <t>RYY8F81</t>
+  </si>
+  <si>
+    <t>SEV7J83</t>
+  </si>
+  <si>
+    <t>JBZ4C34</t>
+  </si>
+  <si>
+    <t>BYZ7824</t>
+  </si>
+  <si>
+    <t>RXY3A23</t>
+  </si>
+  <si>
+    <t>QJP8483</t>
+  </si>
+  <si>
+    <t>GCG6I90</t>
+  </si>
+  <si>
+    <t>QJP8473</t>
+  </si>
+  <si>
+    <t>GZG0005</t>
+  </si>
+  <si>
+    <t>RKY5C07</t>
+  </si>
+  <si>
+    <t>QXD9C76</t>
+  </si>
+  <si>
+    <t>QWA3G46</t>
+  </si>
+  <si>
+    <t>RLK9H99</t>
+  </si>
+  <si>
+    <t>TPL5A08</t>
+  </si>
+  <si>
+    <t>EUR7J14</t>
+  </si>
+  <si>
+    <t>UOK4A59</t>
+  </si>
+  <si>
+    <t>EUT0C13</t>
+  </si>
+  <si>
+    <t>JCC3B22</t>
+  </si>
+  <si>
+    <t>RYC0I06</t>
+  </si>
+  <si>
+    <t>RYC0I76</t>
+  </si>
+  <si>
+    <t>RYA4G49</t>
+  </si>
+  <si>
+    <t>SJL9F08</t>
+  </si>
+  <si>
+    <t>RDB2C27</t>
+  </si>
+  <si>
+    <t>JBO3B22</t>
+  </si>
+  <si>
+    <t>GCN2A21</t>
+  </si>
+  <si>
+    <t>RLA4G55</t>
+  </si>
+  <si>
+    <t>RLI4F49</t>
+  </si>
+  <si>
+    <t>SXJ3C50</t>
+  </si>
+  <si>
+    <t>RYI2I76</t>
+  </si>
+  <si>
+    <t>UCP6C45</t>
+  </si>
+  <si>
+    <t>RAB6H33</t>
+  </si>
+  <si>
+    <t>SEX2A83</t>
+  </si>
+  <si>
+    <t>MIU5C70</t>
+  </si>
+  <si>
+    <t>BEY5I74</t>
+  </si>
+  <si>
+    <t>UBP6C81</t>
+  </si>
+  <si>
+    <t>QMV4G19</t>
+  </si>
+  <si>
+    <t>JDM3C23</t>
+  </si>
+  <si>
+    <t>QJP8443</t>
+  </si>
+  <si>
+    <t>BAM0D51</t>
+  </si>
+  <si>
+    <t>QJP8463</t>
+  </si>
+  <si>
+    <t>RKW5A37</t>
+  </si>
+  <si>
+    <t>RKW6E47</t>
+  </si>
+  <si>
+    <t>KYW2285</t>
+  </si>
+  <si>
+    <t>FUM3F28</t>
+  </si>
+  <si>
+    <t>SEB1I62</t>
+  </si>
+  <si>
+    <t>FCZ3A23</t>
+  </si>
+  <si>
+    <t>SXA4A42</t>
+  </si>
+  <si>
+    <t>QBG1B26</t>
+  </si>
+  <si>
+    <t>QPN0B51</t>
+  </si>
+  <si>
+    <t>VCV0C90</t>
+  </si>
+  <si>
+    <t>OMO8F65</t>
+  </si>
+  <si>
+    <t>BEK0E46</t>
+  </si>
+  <si>
+    <t>RLA3H05</t>
+  </si>
+  <si>
+    <t>AUA8J87</t>
+  </si>
+  <si>
+    <t>RYM2E24</t>
+  </si>
+  <si>
+    <t>- Pendente Frente</t>
+  </si>
+  <si>
+    <t>- Pendente Frente e lateral</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral não mostra o semirreboque por completo, estando cortada na parte frontal.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral não mostra o semirreboque por completo, estando cortado na parte traseira.</t>
+  </si>
+  <si>
+    <t>IA: A imagem está cortada no lado direito, impedindo a visualização do retrovisor direito.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral não exibe a totalidade do conjunto, apresentando corte na parte traseira do segundo semirreboque.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral apresenta cortes na parte superior, não mostrando o semirreboque integralmente.</t>
+  </si>
+  <si>
+    <t>IA: A imagem não exibe a lateral completa do semirreboque, apresentando cortes nas extremidades frontal e traseira.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral não mostra a lateral completa do semirreboque, estando a parte traseira cortada.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral está cortada, não mostrando a lateral completa do semirreboque.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral não mostra a totalidade do semirreboque, estando a parte traseira cortada.</t>
   </si>
 </sst>
 </file>
@@ -1650,7 +1860,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D432"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1673,73 +1884,73 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>46314.343379212965</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>46314.344265925924</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>46314.344538807869</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>46314.430146076389</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>46314.430371365743</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>46314.43061880787</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>46314.430888668983</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
         <v>46314.431844328705</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>46314.432041793982</v>
@@ -1747,10 +1958,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C11" s="1">
         <v>46314.432473437497</v>
@@ -1758,93 +1969,90 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1">
         <v>46314.433658796297</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
         <v>46314.449781134259</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>46314.452003182872</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1">
         <v>46314.452609456021</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
         <v>46314.452804675922</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
         <v>46314.454349247688</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>46314.454706909724</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1">
         <v>46314.454915219911</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1">
         <v>46314.455186793981</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1">
         <v>46314.463670763886</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1">
         <v>46314.465376122687</v>
@@ -1852,34 +2060,34 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1">
         <v>46314.468582164351</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1">
         <v>46314.468819467591</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1">
         <v>46314.470167638887</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1">
         <v>46314.475561412037</v>
@@ -1887,42 +2095,42 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1">
         <v>46314.475915844909</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C28" s="1">
         <v>46314.476109317133</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1">
         <v>46314.476386273149</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1">
         <v>46314.47662898148</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1">
         <v>46314.477258993058</v>
@@ -1930,26 +2138,26 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1">
         <v>46314.477596828707</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C33" s="1">
         <v>46314.477925254629</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C34" s="1">
         <v>46314.478220474535</v>
@@ -1957,34 +2165,34 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1">
         <v>46314.478548356485</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C36" s="1">
         <v>46314.478776331016</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C37" s="1">
         <v>46314.479111805558</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C38" s="1">
         <v>46314.479364409723</v>
@@ -1992,10 +2200,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="1">
         <v>46314.479731643522</v>
@@ -2003,10 +2211,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1">
         <v>46314.480629386577</v>
@@ -2014,10 +2222,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1">
         <v>46314.481955370371</v>
@@ -2025,42 +2233,42 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" s="1">
         <v>46314.482246481479</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C43" s="1">
         <v>46314.505922928241</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C44" s="1">
         <v>46314.503910879626</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C45" s="1">
         <v>46314.504293796293</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C46" s="1">
         <v>46314.505630185187</v>
@@ -2068,66 +2276,66 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C47" s="1">
         <v>46314.503281307872</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C48" s="1">
         <v>46314.50364894676</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C49" s="1">
         <v>46314.505261284721</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C50" s="1">
         <v>46314.506210115738</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C51" s="1">
         <v>46314.506516504633</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C52" s="1">
         <v>46314.559865011572</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C53" s="1">
         <v>46314.560195949074</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C54" s="1">
         <v>46314.561215185182</v>
@@ -2135,34 +2343,34 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C55" s="1">
         <v>46314.561635370374</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C56" s="1">
         <v>46314.562011932867</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C57" s="1">
         <v>46314.562284074076</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C58" s="1">
         <v>46314.562489560187</v>
@@ -2170,98 +2378,98 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1">
         <v>46314.571915532404</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C60" s="1">
         <v>46314.572157372684</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C61" s="1">
         <v>46314.572455150461</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C62" s="1">
         <v>46314.572730046297</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C63" s="1">
         <v>46314.598300254627</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C64" s="1">
         <v>46314.598590972222</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C65" s="1">
         <v>46314.601446747685</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C66" s="1">
         <v>46314.602807627314</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C67" s="1">
         <v>46314.606205520831</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C68" s="1">
         <v>46314.620486747684</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C69" s="1">
         <v>46314.621102777775</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C70" s="1">
         <v>46314.621336377313</v>
@@ -2269,10 +2477,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1">
         <v>46314.621844004629</v>
@@ -2280,26 +2488,26 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="1">
         <v>46314.622419270832</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C73" s="1">
         <v>46314.622722893517</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C74" s="1">
         <v>46314.638474270832</v>
@@ -2307,10 +2515,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C75" s="1">
         <v>46314.638927326392</v>
@@ -2318,136 +2526,130 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="1">
         <v>46314.659938715275</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C77" s="1">
         <v>46314.65943039352</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C78" s="1">
         <v>46314.667878275461</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C79" s="1">
         <v>46314.664233819443</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C80" s="1">
         <v>46314.668099537033</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C81" s="1">
         <v>46314.66982304398</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C82" s="1">
         <v>46314.673438437501</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C83" s="1">
         <v>46314.688068449075</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C84" s="1">
         <v>46314.688350277778</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" t="s">
-        <v>422</v>
+        <v>86</v>
       </c>
       <c r="C85" s="1">
         <v>46314.688814201392</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C86" s="1">
         <v>46314.699540347225</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C87" s="1">
         <v>46314.705863495372</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C88" s="1">
         <v>46315.307201388889</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C89" s="1">
         <v>46315.307658738428</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C90" s="1">
         <v>46315.188505821759</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>94</v>
-      </c>
-      <c r="B91" t="s">
-        <v>423</v>
+        <v>91</v>
       </c>
       <c r="C91" s="1">
         <v>46315.189738518522</v>
@@ -2455,176 +2657,179 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" s="1">
         <v>46315.190148923612</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C93" s="1">
         <v>46315.307961064813</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C94" s="1">
         <v>46315.308393310188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C95" s="1">
         <v>46315.190370601849</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C96" s="1">
         <v>46315.308647534723</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>424</v>
+        <v>4</v>
       </c>
       <c r="C97" s="1">
         <v>46315.190834594905</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D97" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C98" s="1">
         <v>46315.308914201392</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C99" s="1">
         <v>46315.311904490743</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100" s="1">
         <v>46315.316285277775</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C101" s="1">
         <v>46315.316872881944</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C102" s="1">
         <v>46315.356160555559</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C103" s="1">
         <v>46315.361299675926</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C104" s="1">
         <v>46315.364950034724</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C105" s="1">
         <v>46315.379859328707</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C106" s="1">
         <v>46315.381585127318</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C107" s="1">
         <v>46315.401282662038</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C108" s="1">
         <v>46315.400452650465</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C109" s="1">
         <v>46315.400693379626</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C110" s="1">
         <v>46315.401528032409</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C111" s="1">
         <v>46315.402108449074</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C112" s="1">
         <v>46315.402504479163</v>
@@ -2632,125 +2837,122 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C113" s="1">
         <v>46315.410512974537</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C114" s="1">
         <v>46315.435983101852</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C115" s="1">
         <v>46315.436211192129</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C116" s="1">
         <v>46315.437148136574</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C117" s="1">
         <v>46315.445318310187</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C118" s="1">
         <v>46315.444983055553</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
-        <v>119</v>
-      </c>
-      <c r="B119" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C119" s="1">
         <v>46315.44611553241</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C120" s="1">
         <v>46315.446668182871</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C121" s="1">
         <v>46315.446920775466</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C122" s="1">
         <v>46315.451074178243</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C123" s="1">
         <v>46315.461032418978</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C124" s="1">
         <v>46315.460013819444</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C125" s="1">
         <v>46315.460422476855</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C126" s="1">
         <v>46315.461431527779</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C127" s="1">
         <v>46315.461761759259</v>
@@ -2758,130 +2960,130 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B128" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C128" s="1">
         <v>46315.467682951392</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C129" s="1">
         <v>46315.467956053239</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C130" s="1">
         <v>46315.46857715278</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C131" s="1">
         <v>46315.47277453704</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C132" s="1">
         <v>46315.47240027778</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C133" s="1">
         <v>46315.602952361114</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C134" s="1">
         <v>46315.611502662039</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C135" s="1">
         <v>46315.61191146991</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C136" s="1">
         <v>46315.612124409723</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C137" s="1">
         <v>46315.612332534722</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C138" s="1">
         <v>46315.612695277778</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C139" s="1">
         <v>46315.617955243055</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C140" s="1">
         <v>46315.618181087964</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C141" s="1">
         <v>46315.618421041669</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C142" s="1">
         <v>46315.618685636575</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C143" s="1">
         <v>46315.62148396991</v>
@@ -2889,18 +3091,18 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B144" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144" s="1">
         <v>46315.621845590278</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C145" s="1">
         <v>46315.629297638887</v>
@@ -2908,285 +3110,282 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146" s="1">
         <v>46315.630751840275</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C147" s="1">
         <v>46315.631850972219</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C148" s="1">
         <v>46315.602614699077</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C149" s="1">
         <v>46315.600649004627</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C150" s="1">
         <v>46315.599400729167</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C151" s="1">
         <v>46315.598969432867</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C152" s="1">
         <v>46315.598627743057</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C153" s="1">
         <v>46315.598343391204</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C154" s="1">
         <v>46315.59809767361</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C155" s="1">
         <v>46315.597250231483</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C156" s="1">
         <v>46315.595878518521</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C157" s="1">
         <v>46315.597750104163</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C158" s="1">
         <v>46315.632052280096</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C159" s="1">
         <v>46315.606731284723</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C160" s="1">
         <v>46315.603336967593</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C161" s="1">
         <v>46315.606933958334</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C162" s="1">
         <v>46315.632995219908</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C163" s="1">
         <v>46315.633521608797</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C164" s="1">
         <v>46315.633760636571</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C165" s="1">
         <v>46315.633952129632</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C166" s="1">
         <v>46315.643702291665</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C167" s="1">
         <v>46315.643960856483</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C168" s="1">
         <v>46315.64421027778</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C169" s="1">
         <v>46315.644455185182</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C170" s="1">
         <v>46315.644712083333</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C171" s="1">
         <v>46315.64503013889</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C172" s="1">
         <v>46315.645246342596</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C173" s="1">
         <v>46315.645927766207</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C174" s="1">
         <v>46315.646160208336</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C175" s="1">
         <v>46315.647061238429</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C176" s="1">
         <v>46315.675718935185</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C177" s="1">
         <v>46315.675950879631</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C178" s="1">
         <v>46315.676155196757</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
-        <v>176</v>
-      </c>
-      <c r="B179" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="C179" s="1">
         <v>46315.676458194444</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C180" s="1">
         <v>46315.676754259257</v>
@@ -3194,10 +3393,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181" s="1">
         <v>46315.677110810182</v>
@@ -3205,61 +3404,58 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B182" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C182" s="1">
         <v>46315.677539583332</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
-        <v>172</v>
-      </c>
-      <c r="B183" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="C183" s="1">
         <v>46315.670520810185</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C184" s="1">
         <v>46315.664748449075</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C185" s="1">
         <v>46315.678448437502</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C186" s="1">
         <v>46315.678684722225</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C187" s="1">
         <v>46315.679021979166</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C188" s="1">
         <v>46315.687539108796</v>
@@ -3267,26 +3463,26 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B189" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C189" s="1">
         <v>46315.688114641205</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C190" s="1">
         <v>46315.688392245371</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C191" s="1">
         <v>46315.689293344905</v>
@@ -3294,90 +3490,90 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B192" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C192" s="1">
         <v>46315.702383796299</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C193" s="1">
         <v>46315.702604421298</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C194" s="1">
         <v>46315.70288167824</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C195" s="1">
         <v>46315.703119409722</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C196" s="1">
         <v>46315.703412592593</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C197" s="1">
         <v>46315.703642060187</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C198" s="1">
         <v>46315.70399490741</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C199" s="1">
         <v>46316.199406238426</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C200" s="1">
         <v>46316.199700011573</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C201" s="1">
         <v>46316.199913356482</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C202" s="1">
         <v>46316.200284050923</v>
@@ -3385,50 +3581,50 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203" s="1">
         <v>46316.200774502315</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C204" s="1">
         <v>46316.201050532407</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C205" s="1">
         <v>46316.204104282406</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C206" s="1">
         <v>46316.204417048612</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C207" s="1">
         <v>46316.204638900461</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C208" s="1">
         <v>46316.205040428242</v>
@@ -3436,10 +3632,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B209" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C209" s="1">
         <v>46316.206070752312</v>
@@ -3447,74 +3643,74 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C210" s="1">
         <v>46316.20542096065</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C211" s="1">
         <v>46316.205696041667</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C212" s="1">
         <v>46316.206302395833</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C213" s="1">
         <v>46316.311312928243</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C214" s="1">
         <v>46316.319413090278</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C215" s="1">
         <v>46316.319660381945</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C216" s="1">
         <v>46316.319883738426</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C217" s="1">
         <v>46316.320096365744</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C218" s="1">
         <v>46316.320386122687</v>
@@ -3522,34 +3718,34 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B219" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C219" s="1">
         <v>46316.320744652781</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C220" s="1">
         <v>46316.351928657408</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C221" s="1">
         <v>46316.352207048614</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C222" s="1">
         <v>46316.353439050923</v>
@@ -3557,50 +3753,50 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B223" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C223" s="1">
         <v>46316.354008576389</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C224" s="1">
         <v>46316.378215949073</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C225" s="1">
         <v>46316.378446087961</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C226" s="1">
         <v>46316.387992719909</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C227" s="1">
         <v>46316.388226782408</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C228" s="1">
         <v>46316.388481967595</v>
@@ -3608,787 +3804,790 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B229" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229" s="1">
         <v>46316.388817384257</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C230" s="1">
         <v>46316.389074282408</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C231" s="1">
         <v>46316.441358449076</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C232" s="1">
         <v>46316.441555578705</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C233" s="1">
         <v>46316.441775243053</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C234" s="1">
         <v>46316.442184976855</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C235" s="1">
         <v>46316.442407916664</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" t="s">
-        <v>229</v>
-      </c>
-      <c r="B236" t="s">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="C236" s="1">
         <v>46316.442784560182</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C237" s="1">
         <v>46316.443086388892</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C238" s="1">
         <v>46316.443402303237</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C239" s="1">
         <v>46316.444558564814</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C240" s="1">
         <v>46316.444823356484</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C241" s="1">
         <v>46316.445036643519</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C242" s="1">
         <v>46316.445316921294</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C243" s="1">
         <v>46316.445764259261</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C244" s="1">
         <v>46316.445975000002</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C245" s="1">
         <v>46316.447001851855</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C246" s="1">
         <v>46316.447213692132</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C247" s="1">
         <v>46316.447439699077</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C248" s="1">
         <v>46316.455675833335</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C249" s="1">
         <v>46316.455994398151</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C250" s="1">
         <v>46316.457338067128</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C251" s="1">
         <v>46316.457579085647</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C252" s="1">
         <v>46316.458141215277</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C253" s="1">
         <v>46316.457114062498</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C254" s="1">
         <v>46316.456601111109</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C255" s="1">
         <v>46316.45631303241</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C256" s="1">
         <v>46316.466048125003</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C257" s="1">
         <v>46316.490917766205</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C258" s="1">
         <v>46316.491217511575</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C259" s="1">
         <v>46316.491495995368</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C260" s="1">
         <v>46316.533674479164</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C261" s="1">
         <v>46316.533987164352</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C262" s="1">
         <v>46316.534203668984</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C263" s="1">
         <v>46316.534398379627</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C264" s="1">
         <v>46316.534599930557</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C265" s="1">
         <v>46316.534813240738</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C266" s="1">
         <v>46316.535017638889</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B267" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C267" s="1">
         <v>46316.547602592589</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C268" s="1">
         <v>46316.548042326387</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B269" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C269" s="1">
         <v>46316.562436898152</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B270" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C270" s="1">
         <v>46316.563351701392</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D270" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C271" s="1">
         <v>46316.602650578701</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C272" s="1">
         <v>46316.602956678238</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C273" s="1">
         <v>46316.603981203705</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C274" s="1">
         <v>46316.604509456018</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C275" s="1">
         <v>46316.606905671295</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C276" s="1">
         <v>46316.607432060184</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C277" s="1">
         <v>46316.607675231484</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C278" s="1">
         <v>46316.607885486112</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C279" s="1">
         <v>46316.608197928239</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C280" s="1">
         <v>46316.608412546295</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C281" s="1">
         <v>46316.608644502317</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C282" s="1">
         <v>46316.608937581019</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C283" s="1">
         <v>46316.609175358797</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C284" s="1">
         <v>46316.609416643521</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B285" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C285" s="1">
         <v>46316.609844062499</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D285" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C286" s="1">
         <v>46316.610071550924</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C287" s="1">
         <v>46316.610292754631</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C288" s="1">
         <v>46316.610534733794</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C289" s="1">
         <v>46316.610766342594</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C290" s="1">
         <v>46316.61153115741</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C291" s="1">
         <v>46316.649323703707</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C292" s="1">
         <v>46316.649948368053</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C293" s="1">
         <v>46316.649855474534</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C294" s="1">
         <v>46316.650880636575</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C295" s="1">
         <v>46316.650432349539</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C296" s="1">
         <v>46316.650694236108</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C297" s="1">
         <v>46316.651207800925</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C298" s="1">
         <v>46316.651510254633</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C299" s="1">
         <v>46316.651764166665</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C300" s="1">
         <v>46316.652571805556</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B301" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301" s="1">
         <v>46316.652862719908</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D301" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" t="s">
-        <v>293</v>
-      </c>
-      <c r="B302" t="s">
-        <v>4</v>
+        <v>290</v>
       </c>
       <c r="C302" s="1">
         <v>46316.653333506947</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C303" s="1">
         <v>46316.655844687499</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C304" s="1">
         <v>46316.656401759261</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C305" s="1">
         <v>46316.662931944447</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C306" s="1">
         <v>46316.659392928239</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C307" s="1">
         <v>46316.659700798613</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" t="s">
-        <v>299</v>
-      </c>
-      <c r="B308" t="s">
-        <v>4</v>
+        <v>296</v>
       </c>
       <c r="C308" s="1">
         <v>46316.655490196761</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B309" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C309" s="1">
         <v>46316.660021215277</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C310" s="1">
         <v>46316.663523344905</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C311" s="1">
         <v>46316.66397306713</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C312" s="1">
         <v>46316.655218993059</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C313" s="1">
         <v>46316.664194849538</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B314" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C314" s="1">
         <v>46316.66474547454</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C315" s="1">
         <v>46316.665075289355</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C316" s="1">
         <v>46316.665315798607</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C317" s="1">
         <v>46316.665554606479</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C318" s="1">
         <v>46316.666150277779</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C319" s="1">
         <v>46316.666769861113</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B320" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C320" s="1">
         <v>46316.66728306713</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D320" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C321" s="1">
         <v>46316.667589375</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C322" s="1">
         <v>46316.681021215278</v>
@@ -4396,42 +4595,42 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B323" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C323" s="1">
         <v>46317.34018446759</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C324" s="1">
         <v>46317.350805567126</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C325" s="1">
         <v>46317.350040347221</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C326" s="1">
         <v>46317.349033449071</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C327" s="1">
         <v>46317.348731574071</v>
@@ -4439,58 +4638,58 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B328" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C328" s="1">
         <v>46317.348020972226</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C329" s="1">
         <v>46317.348241458334</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C330" s="1">
         <v>46317.347743738428</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C331" s="1">
         <v>46317.350477280095</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C332" s="1">
         <v>46317.347308449076</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C333" s="1">
         <v>46317.345922685185</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C334" s="1">
         <v>46317.348444016206</v>
@@ -4498,18 +4697,18 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B335" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C335" s="1">
         <v>46317.346541550927</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C336" s="1">
         <v>46317.345620856482</v>
@@ -4517,90 +4716,87 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" t="s">
-        <v>328</v>
-      </c>
-      <c r="B337" t="s">
-        <v>7</v>
+        <v>325</v>
       </c>
       <c r="C337" s="1">
         <v>46317.345109942129</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C338" s="1">
         <v>46317.346153784725</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C339" s="1">
         <v>46317.344782118053</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C340" s="1">
         <v>46317.344479212959</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C341" s="1">
         <v>46317.343963506944</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C342" s="1">
         <v>46317.345313055557</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C343" s="1">
         <v>46317.344191875003</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C344" s="1">
         <v>46317.346821921295</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C345" s="1">
         <v>46317.349823645833</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C346" s="1">
         <v>46317.351432847223</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C347" s="1">
         <v>46317.350254502315</v>
@@ -4608,10 +4804,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B348" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C348" s="1">
         <v>46317.351190266207</v>
@@ -4619,10 +4815,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B349" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C349" s="1">
         <v>46317.351794768518</v>
@@ -4630,10 +4826,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" t="s">
-        <v>341</v>
-      </c>
-      <c r="B350" t="s">
-        <v>7</v>
+        <v>338</v>
       </c>
       <c r="C350" s="1">
         <v>46317.364638946761</v>
@@ -4641,177 +4834,183 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B351" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C351" s="1">
         <v>46317.363271354166</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C352" s="1">
         <v>46317.368958587962</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C353" s="1">
         <v>46317.369462361108</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B354" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C354" s="1">
         <v>46317.391570717591</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="D354" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C355" s="1">
         <v>46317.391111435187</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C356" s="1">
         <v>46317.398353379627</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C357" s="1">
         <v>46317.41721107639</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C358" s="1">
         <v>46317.406281446762</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C359" s="1">
         <v>46317.415765983795</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C360" s="1">
         <v>46317.416297141201</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C361" s="1">
         <v>46317.41667525463</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B362" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C362" s="1">
         <v>46317.417663981483</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C363" s="1">
         <v>46317.419560358794</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C364" s="1">
         <v>46317.42893991898</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B365" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C365" s="1">
         <v>46317.429868819447</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C366" s="1">
         <v>46317.430422754631</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C367" s="1">
         <v>46317.443914178242</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B368" t="s">
-        <v>424</v>
+        <v>4</v>
       </c>
       <c r="C368" s="1">
         <v>46317.444625289354</v>
       </c>
+      <c r="D368" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B369" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C369" s="1">
         <v>46317.445218726854</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C370" s="1">
         <v>46317.445474085645</v>
@@ -4819,10 +5018,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B371" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C371" s="1">
         <v>46317.448277870368</v>
@@ -4830,26 +5029,26 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B372" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C372" s="1">
         <v>46317.449088368056</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C373" s="1">
         <v>46317.448752662036</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C374" s="1">
         <v>46317.450627893515</v>
@@ -4857,26 +5056,26 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B375" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C375" s="1">
         <v>46317.45133329861</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C376" s="1">
         <v>46317.451688761575</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C377" s="1">
         <v>46317.45721439815</v>
@@ -4884,26 +5083,26 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B378" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C378" s="1">
         <v>46317.465697962965</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C379" s="1">
         <v>46317.466039166669</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C380" s="1">
         <v>46317.467295752314</v>
@@ -4911,26 +5110,26 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B381" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C381" s="1">
         <v>46317.46762891204</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C382" s="1">
         <v>46317.467955578701</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C383" s="1">
         <v>46317.468422928243</v>
@@ -4938,29 +5137,26 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B384" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C384" s="1">
         <v>46317.475458680557</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C385" s="1">
         <v>46317.47680895833</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" t="s">
-        <v>375</v>
-      </c>
-      <c r="B386" t="s">
-        <v>8</v>
+        <v>372</v>
       </c>
       <c r="C386" s="1">
         <v>46317.485485428238</v>
@@ -4968,18 +5164,18 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B387" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C387" s="1">
         <v>46317.484748391202</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C388" s="1">
         <v>46317.485016342594</v>
@@ -4987,58 +5183,58 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B389" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C389" s="1">
         <v>46317.485875254628</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C390" s="1">
         <v>46317.486205717592</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C391" s="1">
         <v>46317.48728079861</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C392" s="1">
         <v>46317.487546087963</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C393" s="1">
         <v>46317.508724675929</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C394" s="1">
         <v>46317.508313055558</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C395" s="1">
         <v>46317.508978761573</v>
@@ -5046,42 +5242,42 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B396" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C396" s="1">
         <v>46317.524752314814</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C397" s="1">
         <v>46317.559528425925</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C398" s="1">
         <v>46317.559787638886</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C399" s="1">
         <v>46317.561094143515</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C400" s="1">
         <v>46317.5616090162</v>
@@ -5089,18 +5285,18 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B401" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C401" s="1">
         <v>46317.566485555559</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C402" s="1">
         <v>46317.580779398151</v>
@@ -5108,98 +5304,98 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B403" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C403" s="1">
         <v>46317.581182627313</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C404" s="1">
         <v>46317.590580694443</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C405" s="1">
         <v>46317.589558506945</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C406" s="1">
         <v>46317.589234270832</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C407" s="1">
         <v>46317.589938356483</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C408" s="1">
         <v>46317.59126212963</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C409" s="1">
         <v>46317.610700567129</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C410" s="1">
         <v>46317.610324675923</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C411" s="1">
         <v>46317.612850925929</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C412" s="1">
         <v>46317.640879293984</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C413" s="1">
         <v>46317.641344768519</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C414" s="1">
         <v>46317.649486342591</v>
@@ -5207,90 +5403,90 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B415" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C415" s="1">
         <v>46317.654907002317</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C416" s="1">
         <v>46317.654567361111</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C417" s="1">
         <v>46317.655494780091</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C418" s="1">
         <v>46317.665912233795</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C419" s="1">
         <v>46317.669549907405</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C420" s="1">
         <v>46317.673811365741</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C421" s="1">
         <v>46317.675059965281</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C422" s="1">
         <v>46317.678380057871</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C423" s="1">
         <v>46317.688480925928</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C424" s="1">
         <v>46317.688784965278</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C425" s="1">
         <v>46317.68918872685</v>
@@ -5298,10 +5494,10 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B426" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C426" s="1">
         <v>46317.700926215279</v>
@@ -5309,56 +5505,635 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B427" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C427" s="1">
         <v>46317.70125471065</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C428" s="1">
         <v>46317.701605613423</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C429" s="1">
         <v>46317.702259745369</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C430" s="1">
         <v>46318.189411504631</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C431" s="1">
         <v>46317.713062199073</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C432" s="1">
         <v>46317.720143217593</v>
       </c>
     </row>
+    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A433" t="s">
+        <v>424</v>
+      </c>
+      <c r="C433" s="1">
+        <v>46318.379348645831</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A434" t="s">
+        <v>425</v>
+      </c>
+      <c r="C434" s="1">
+        <v>46318.381625682872</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A435" t="s">
+        <v>426</v>
+      </c>
+      <c r="B435" t="s">
+        <v>5</v>
+      </c>
+      <c r="C435" s="1">
+        <v>46318.380333877314</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A436" t="s">
+        <v>427</v>
+      </c>
+      <c r="B436" t="s">
+        <v>418</v>
+      </c>
+      <c r="C436" s="1">
+        <v>46318.380657002315</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A437" t="s">
+        <v>428</v>
+      </c>
+      <c r="C437" s="1">
+        <v>46318.389500694444</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A438" t="s">
+        <v>429</v>
+      </c>
+      <c r="C438" s="1">
+        <v>46318.390437037036</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A439" t="s">
+        <v>430</v>
+      </c>
+      <c r="B439" t="s">
+        <v>488</v>
+      </c>
+      <c r="C439" s="1">
+        <v>46318.3907421412</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A440" t="s">
+        <v>431</v>
+      </c>
+      <c r="C440" s="1">
+        <v>46318.382043310186</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A441" t="s">
+        <v>432</v>
+      </c>
+      <c r="B441" t="s">
+        <v>5</v>
+      </c>
+      <c r="C441" s="1">
+        <v>46318.382311851848</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A442" t="s">
+        <v>433</v>
+      </c>
+      <c r="C442" s="1">
+        <v>46318.388368819447</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A443" t="s">
+        <v>434</v>
+      </c>
+      <c r="B443" t="s">
+        <v>489</v>
+      </c>
+      <c r="C443" s="1">
+        <v>46318.391407442126</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A444" t="s">
+        <v>435</v>
+      </c>
+      <c r="C444" s="1">
+        <v>46318.39166090278</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A445" t="s">
+        <v>436</v>
+      </c>
+      <c r="C445" s="1">
+        <v>46318.392170902778</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A446" t="s">
+        <v>437</v>
+      </c>
+      <c r="C446" s="1">
+        <v>46318.392382523147</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A447" t="s">
+        <v>438</v>
+      </c>
+      <c r="C447" s="1">
+        <v>46318.393054537039</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A448" t="s">
+        <v>439</v>
+      </c>
+      <c r="C448" s="1">
+        <v>46318.393303541663</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A449" t="s">
+        <v>440</v>
+      </c>
+      <c r="C449" s="1">
+        <v>46318.393715428239</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A450" t="s">
+        <v>441</v>
+      </c>
+      <c r="C450" s="1">
+        <v>46318.393936250002</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A451" t="s">
+        <v>442</v>
+      </c>
+      <c r="B451" t="s">
+        <v>4</v>
+      </c>
+      <c r="C451" s="1">
+        <v>46318.405059398145</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A452" t="s">
+        <v>443</v>
+      </c>
+      <c r="C452" s="1">
+        <v>46318.405408715276</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A453" t="s">
+        <v>444</v>
+      </c>
+      <c r="B453" t="s">
+        <v>4</v>
+      </c>
+      <c r="C453" s="1">
+        <v>46318.40583358796</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A454" t="s">
+        <v>445</v>
+      </c>
+      <c r="C454" s="1">
+        <v>46318.427280868054</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A455" t="s">
+        <v>446</v>
+      </c>
+      <c r="C455" s="1">
+        <v>46318.427044699078</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A456" t="s">
+        <v>447</v>
+      </c>
+      <c r="C456" s="1">
+        <v>46318.426807314812</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A457" t="s">
+        <v>448</v>
+      </c>
+      <c r="C457" s="1">
+        <v>46318.427580231481</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A458" t="s">
+        <v>449</v>
+      </c>
+      <c r="C458" s="1">
+        <v>46318.427793194445</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A459" t="s">
+        <v>450</v>
+      </c>
+      <c r="C459" s="1">
+        <v>46318.432990428242</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A460" t="s">
+        <v>451</v>
+      </c>
+      <c r="B460" t="s">
+        <v>5</v>
+      </c>
+      <c r="C460" s="1">
+        <v>46318.433417129629</v>
+      </c>
+      <c r="D460" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A461" t="s">
+        <v>452</v>
+      </c>
+      <c r="B461" t="s">
+        <v>5</v>
+      </c>
+      <c r="C461" s="1">
+        <v>46318.439424571756</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A462" t="s">
+        <v>453</v>
+      </c>
+      <c r="C462" s="1">
+        <v>46318.443270636577</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A463" t="s">
+        <v>454</v>
+      </c>
+      <c r="C463" s="1">
+        <v>46318.490852650466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A464" t="s">
+        <v>455</v>
+      </c>
+      <c r="C464" s="1">
+        <v>46318.491102314816</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A465" t="s">
+        <v>456</v>
+      </c>
+      <c r="C465" s="1">
+        <v>46318.490891666668</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A466" t="s">
+        <v>457</v>
+      </c>
+      <c r="C466" s="1">
+        <v>46318.490296215277</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A467" t="s">
+        <v>458</v>
+      </c>
+      <c r="C467" s="1">
+        <v>46318.491128368056</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A468" t="s">
+        <v>459</v>
+      </c>
+      <c r="C468" s="1">
+        <v>46318.491340925924</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A469" t="s">
+        <v>460</v>
+      </c>
+      <c r="C469" s="1">
+        <v>46318.492865347223</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A470" t="s">
+        <v>461</v>
+      </c>
+      <c r="B470" t="s">
+        <v>5</v>
+      </c>
+      <c r="C470" s="1">
+        <v>46318.491616828702</v>
+      </c>
+      <c r="D470" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A471" t="s">
+        <v>462</v>
+      </c>
+      <c r="C471" s="1">
+        <v>46318.494003402775</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A472" t="s">
+        <v>463</v>
+      </c>
+      <c r="C472" s="1">
+        <v>46318.493984884262</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A473" t="s">
+        <v>464</v>
+      </c>
+      <c r="C473" s="1">
+        <v>46318.503831469905</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A474" t="s">
+        <v>465</v>
+      </c>
+      <c r="C474" s="1">
+        <v>46318.504232881947</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A475" t="s">
+        <v>466</v>
+      </c>
+      <c r="C475" s="1">
+        <v>46318.52962050926</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A476" t="s">
+        <v>467</v>
+      </c>
+      <c r="C476" s="1">
+        <v>46318.530970740743</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A477" t="s">
+        <v>468</v>
+      </c>
+      <c r="C477" s="1">
+        <v>46318.565858321759</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A478" t="s">
+        <v>469</v>
+      </c>
+      <c r="C478" s="1">
+        <v>46318.575484629633</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A479" t="s">
+        <v>470</v>
+      </c>
+      <c r="B479" t="s">
+        <v>4</v>
+      </c>
+      <c r="C479" s="1">
+        <v>46318.583952372683</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A480" t="s">
+        <v>471</v>
+      </c>
+      <c r="C480" s="1">
+        <v>46318.584380127315</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A481" t="s">
+        <v>472</v>
+      </c>
+      <c r="B481" t="s">
+        <v>4</v>
+      </c>
+      <c r="C481" s="1">
+        <v>46318.584904340278</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A482" t="s">
+        <v>473</v>
+      </c>
+      <c r="B482" t="s">
+        <v>5</v>
+      </c>
+      <c r="C482" s="1">
+        <v>46318.614888750002</v>
+      </c>
+      <c r="D482" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A483" t="s">
+        <v>474</v>
+      </c>
+      <c r="B483" t="s">
+        <v>5</v>
+      </c>
+      <c r="C483" s="1">
+        <v>46318.614326608797</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A484" t="s">
+        <v>475</v>
+      </c>
+      <c r="C484" s="1">
+        <v>46318.614601331021</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A485" t="s">
+        <v>476</v>
+      </c>
+      <c r="C485" s="1">
+        <v>46318.614003946757</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A486" t="s">
+        <v>477</v>
+      </c>
+      <c r="B486" t="s">
+        <v>5</v>
+      </c>
+      <c r="C486" s="1">
+        <v>46318.615288530091</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A487" t="s">
+        <v>478</v>
+      </c>
+      <c r="C487" s="1">
+        <v>46318.615708101854</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A488" t="s">
+        <v>479</v>
+      </c>
+      <c r="C488" s="1">
+        <v>46318.620106828705</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A489" t="s">
+        <v>480</v>
+      </c>
+      <c r="C489" s="1">
+        <v>46318.623910833332</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A490" t="s">
+        <v>481</v>
+      </c>
+      <c r="C490" s="1">
+        <v>46318.626468298608</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A491" t="s">
+        <v>482</v>
+      </c>
+      <c r="C491" s="1">
+        <v>46318.635854305554</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A492" t="s">
+        <v>483</v>
+      </c>
+      <c r="C492" s="1">
+        <v>46318.636147372687</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A493" t="s">
+        <v>484</v>
+      </c>
+      <c r="C493" s="1">
+        <v>46318.636435879627</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A494" t="s">
+        <v>485</v>
+      </c>
+      <c r="C494" s="1">
+        <v>46318.646399155092</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A495" t="s">
+        <v>486</v>
+      </c>
+      <c r="C495" s="1">
+        <v>46318.64666421296</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A496" t="s">
+        <v>487</v>
+      </c>
+      <c r="C496" s="1">
+        <v>46318.651625798608</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D496" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{96a13d59-91c6-41b6-a5fa-a0e17fd4925a}" enabled="0" method="" siteId="{96a13d59-91c6-41b6-a5fa-a0e17fd4925a}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/dados/ambev-spot-t1.xlsx
+++ b/dados/ambev-spot-t1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupodemarco-my.sharepoint.com/personal/tallison_jesus_demarco_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{8D22D165-2D9C-4516-9ADF-B65891E08959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A648F1-ECFC-4969-8137-B3EC14F4F32A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{8D22D165-2D9C-4516-9ADF-B65891E08959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF6F4E9D-4ECA-43D0-AEEC-51AEBC2309AA}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$D$496</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="495">
   <si>
     <t>Identificador</t>
   </si>
@@ -1288,15 +1301,6 @@
     <t>-  Lateral</t>
   </si>
   <si>
-    <t>Bug pendente Frente</t>
-  </si>
-  <si>
-    <t>BUG pendente frente</t>
-  </si>
-  <si>
-    <t>Bug pendente Frente e Lateral</t>
-  </si>
-  <si>
     <t>RKZ6I31</t>
   </si>
   <si>
@@ -1489,12 +1493,6 @@
     <t>RYM2E24</t>
   </si>
   <si>
-    <t>- Pendente Frente</t>
-  </si>
-  <si>
-    <t>- Pendente Frente e lateral</t>
-  </si>
-  <si>
     <t>IA: A imagem lateral não mostra o semirreboque por completo, estando cortada na parte frontal.</t>
   </si>
   <si>
@@ -1520,6 +1518,9 @@
   </si>
   <si>
     <t>IA: A imagem lateral não mostra a totalidade do semirreboque, estando a parte traseira cortada.</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1861,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D496"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>46314.343379212965</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>46314.344265925924</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>46314.344538807869</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>46314.430146076389</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>46314.430371365743</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>46314.43061880787</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>46314.430888668983</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>46314.431844328705</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>46314.433658796297</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>46314.449781134259</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>46314.452003182872</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>46314.452609456021</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>46314.452804675922</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>46314.454349247688</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>46314.454706909724</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>46314.454915219911</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>46314.455186793981</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>46314.463670763886</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>46314.468582164351</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>46314.468819467591</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>46314.470167638887</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>46314.475915844909</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>46314.476109317133</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>46314.476386273149</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>46314.47662898148</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>46314.477596828707</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>46314.477925254629</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>46314.478548356485</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>46314.478776331016</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>46314.479111805558</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>46314.482246481479</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>46314.505922928241</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>46314.503910879626</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>46314.504293796293</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>46314.503281307872</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>46314.50364894676</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>46314.505261284721</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>46314.506210115738</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>46314.506516504633</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>46314.559865011572</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>46314.560195949074</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>46314.561635370374</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>46314.562011932867</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>46314.562284074076</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>46314.571915532404</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>46314.572157372684</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>46314.572455150461</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>46314.572730046297</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>46314.598300254627</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>46314.598590972222</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>46314.601446747685</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>46314.602807627314</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>46314.606205520831</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>46314.620486747684</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>46314.621102777775</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>46314.622419270832</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>46314.622722893517</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>46314.659938715275</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>46314.65943039352</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>46314.667878275461</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>46314.664233819443</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>46314.668099537033</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>46314.66982304398</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>46314.673438437501</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>46314.688068449075</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>46314.688350277778</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>46314.688814201392</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>46314.699540347225</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>46314.705863495372</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>46315.307201388889</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>46315.307658738428</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>46315.188505821759</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>46315.190148923612</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>46315.307961064813</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>46315.308393310188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>46315.190370601849</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>86</v>
       </c>
@@ -2709,10 +2709,10 @@
         <v>46315.190834594905</v>
       </c>
       <c r="D97" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>46315.308914201392</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>46315.316285277775</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>46315.316872881944</v>
       </c>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>46315.356160555559</v>
       </c>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>46315.361299675926</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>96</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>46315.364950034724</v>
       </c>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>46315.379859328707</v>
       </c>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>46315.381585127318</v>
       </c>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>46315.401282662038</v>
       </c>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>86</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>46315.400452650465</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>106</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>46315.400693379626</v>
       </c>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>46315.401528032409</v>
       </c>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>108</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>46315.402108449074</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>109</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>46315.410512974537</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>111</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>46315.435983101852</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>112</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>46315.436211192129</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>113</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>46315.437148136574</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>114</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>46315.445318310187</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>115</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>46315.444983055553</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>116</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>46315.44611553241</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>117</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>46315.446668182871</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>118</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>46315.446920775466</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>46315.451074178243</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>46315.461032418978</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>121</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>46315.460013819444</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>122</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>46315.460422476855</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>123</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>46315.461431527779</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>124</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>46315.467682951392</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>126</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>46315.467956053239</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>46315.46857715278</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>128</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>46315.47277453704</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>46315.47240027778</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>46315.602952361114</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>131</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>46315.611502662039</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>46315.61191146991</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>133</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>46315.612124409723</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>134</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>46315.612332534722</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>135</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>46315.612695277778</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>136</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>46315.617955243055</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>137</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>46315.618181087964</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>138</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>46315.618421041669</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>46315.618685636575</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>140</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>46315.621845590278</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>142</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>46315.630751840275</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>139</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>46315.631850972219</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>143</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>46315.602614699077</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>141</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>46315.600649004627</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>144</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>46315.599400729167</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>145</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>46315.598969432867</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>146</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>46315.598627743057</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>147</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>46315.598343391204</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>148</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>46315.59809767361</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>149</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>46315.597250231483</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>150</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>46315.595878518521</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>151</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>46315.597750104163</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>152</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>46315.632052280096</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>153</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>46315.606731284723</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>154</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>46315.603336967593</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>155</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>46315.606933958334</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>156</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>46315.632995219908</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>157</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>46315.633521608797</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>158</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>46315.633760636571</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>159</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>46315.633952129632</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>160</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>46315.643702291665</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>161</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>46315.643960856483</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>162</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>46315.64421027778</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>163</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>46315.644455185182</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>164</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>46315.644712083333</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>165</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>46315.64503013889</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>166</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>46315.645246342596</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>167</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>46315.645927766207</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>168</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>46315.646160208336</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>169</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>46315.647061238429</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>170</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>46315.675718935185</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>171</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>46315.675950879631</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>172</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>46315.676155196757</v>
       </c>
     </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>173</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>46315.676458194444</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
         <v>174</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>46315.677539583332</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
         <v>169</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>46315.670520810185</v>
       </c>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
         <v>169</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>46315.664748449075</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
         <v>177</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>46315.678448437502</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
         <v>178</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>46315.678684722225</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
         <v>179</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>46315.679021979166</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
         <v>180</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>46315.688114641205</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
         <v>179</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>46315.688392245371</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
         <v>182</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>46315.702383796299</v>
       </c>
     </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
         <v>184</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>46315.702604421298</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
         <v>185</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>46315.70288167824</v>
       </c>
     </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
         <v>186</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>46315.703119409722</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>187</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>46315.703412592593</v>
       </c>
     </row>
-    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>188</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>46315.703642060187</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>189</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>46315.70399490741</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
         <v>190</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>46316.199406238426</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>191</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>46316.199700011573</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>192</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>46316.199913356482</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
         <v>193</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>46316.200774502315</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>195</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>46316.201050532407</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" t="s">
         <v>196</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>46316.204104282406</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" t="s">
         <v>197</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>46316.204417048612</v>
       </c>
     </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" t="s">
         <v>198</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>46316.204638900461</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
         <v>199</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>46316.20542096065</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>202</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>46316.205696041667</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
         <v>203</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>46316.206302395833</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
         <v>204</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>46316.311312928243</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" t="s">
         <v>205</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>46316.319413090278</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" t="s">
         <v>206</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>46316.319660381945</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" t="s">
         <v>207</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>46316.319883738426</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" t="s">
         <v>86</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>46316.320096365744</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" t="s">
         <v>208</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>46316.320744652781</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" t="s">
         <v>210</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>46316.351928657408</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" t="s">
         <v>211</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>46316.352207048614</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" t="s">
         <v>212</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>46316.354008576389</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" t="s">
         <v>214</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>46316.378215949073</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" t="s">
         <v>215</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>46316.378446087961</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" t="s">
         <v>216</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>46316.387992719909</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" t="s">
         <v>217</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>46316.388226782408</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" t="s">
         <v>218</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>46316.388817384257</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" t="s">
         <v>220</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>46316.389074282408</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" t="s">
         <v>221</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>46316.441358449076</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" t="s">
         <v>222</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>46316.441555578705</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" t="s">
         <v>223</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>46316.441775243053</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" t="s">
         <v>224</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>46316.442184976855</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" t="s">
         <v>225</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>46316.442407916664</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" t="s">
         <v>226</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>46316.442784560182</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" t="s">
         <v>227</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>46316.443086388892</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" t="s">
         <v>228</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>46316.443402303237</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" t="s">
         <v>229</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>46316.444558564814</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" t="s">
         <v>230</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>46316.444823356484</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" t="s">
         <v>231</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>46316.445036643519</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" t="s">
         <v>232</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>46316.445316921294</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" t="s">
         <v>233</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>46316.445764259261</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" t="s">
         <v>234</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>46316.445975000002</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" t="s">
         <v>235</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>46316.447001851855</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" t="s">
         <v>236</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>46316.447213692132</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" t="s">
         <v>237</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>46316.447439699077</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" t="s">
         <v>238</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>46316.455675833335</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" t="s">
         <v>239</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>46316.455994398151</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" t="s">
         <v>240</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>46316.457338067128</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" t="s">
         <v>241</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>46316.457579085647</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" t="s">
         <v>242</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>46316.458141215277</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" t="s">
         <v>243</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>46316.457114062498</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" t="s">
         <v>244</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>46316.456601111109</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" t="s">
         <v>245</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>46316.45631303241</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" t="s">
         <v>246</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>46316.466048125003</v>
       </c>
     </row>
-    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" t="s">
         <v>247</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>46316.490917766205</v>
       </c>
     </row>
-    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" t="s">
         <v>248</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>46316.491217511575</v>
       </c>
     </row>
-    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" t="s">
         <v>249</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>46316.491495995368</v>
       </c>
     </row>
-    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" t="s">
         <v>250</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>46316.533674479164</v>
       </c>
     </row>
-    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" t="s">
         <v>251</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>46316.533987164352</v>
       </c>
     </row>
-    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" t="s">
         <v>252</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>46316.534203668984</v>
       </c>
     </row>
-    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" t="s">
         <v>253</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>46316.534398379627</v>
       </c>
     </row>
-    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" t="s">
         <v>209</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>46316.534599930557</v>
       </c>
     </row>
-    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" t="s">
         <v>254</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>46316.534813240738</v>
       </c>
     </row>
-    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" t="s">
         <v>255</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>46316.547602592589</v>
       </c>
     </row>
-    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" t="s">
         <v>257</v>
       </c>
@@ -4150,10 +4150,10 @@
         <v>46316.563351701392</v>
       </c>
       <c r="D270" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" t="s">
         <v>260</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>46316.602650578701</v>
       </c>
     </row>
-    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" t="s">
         <v>261</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>46316.602956678238</v>
       </c>
     </row>
-    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
         <v>262</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>46316.603981203705</v>
       </c>
     </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" t="s">
         <v>263</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>46316.604509456018</v>
       </c>
     </row>
-    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" t="s">
         <v>264</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>46316.606905671295</v>
       </c>
     </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" t="s">
         <v>265</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>46316.607432060184</v>
       </c>
     </row>
-    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" t="s">
         <v>266</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>46316.607675231484</v>
       </c>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" t="s">
         <v>267</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>46316.607885486112</v>
       </c>
     </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" t="s">
         <v>268</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>46316.608197928239</v>
       </c>
     </row>
-    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" t="s">
         <v>269</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>46316.608412546295</v>
       </c>
     </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" t="s">
         <v>270</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>46316.608644502317</v>
       </c>
     </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" t="s">
         <v>271</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>46316.608937581019</v>
       </c>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" t="s">
         <v>272</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>46316.609175358797</v>
       </c>
     </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" t="s">
         <v>273</v>
       </c>
@@ -4276,10 +4276,10 @@
         <v>46316.609844062499</v>
       </c>
       <c r="D285" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" t="s">
         <v>275</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>46316.610071550924</v>
       </c>
     </row>
-    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" t="s">
         <v>276</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>46316.610292754631</v>
       </c>
     </row>
-    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" t="s">
         <v>277</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>46316.610534733794</v>
       </c>
     </row>
-    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" t="s">
         <v>278</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>46316.610766342594</v>
       </c>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" t="s">
         <v>279</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>46316.61153115741</v>
       </c>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" t="s">
         <v>280</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>46316.649323703707</v>
       </c>
     </row>
-    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" t="s">
         <v>281</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>46316.649948368053</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" t="s">
         <v>282</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>46316.649855474534</v>
       </c>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" t="s">
         <v>283</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>46316.650880636575</v>
       </c>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" t="s">
         <v>204</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>46316.650432349539</v>
       </c>
     </row>
-    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" t="s">
         <v>284</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>46316.650694236108</v>
       </c>
     </row>
-    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" t="s">
         <v>285</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>46316.651207800925</v>
       </c>
     </row>
-    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" t="s">
         <v>286</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>46316.651510254633</v>
       </c>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" t="s">
         <v>287</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>46316.651764166665</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" t="s">
         <v>288</v>
       </c>
@@ -4410,10 +4410,10 @@
         <v>46316.652862719908</v>
       </c>
       <c r="D301" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" t="s">
         <v>290</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>46316.653333506947</v>
       </c>
     </row>
-    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" t="s">
         <v>291</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>46316.655844687499</v>
       </c>
     </row>
-    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" t="s">
         <v>292</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>46316.656401759261</v>
       </c>
     </row>
-    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" t="s">
         <v>293</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>46316.662931944447</v>
       </c>
     </row>
-    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" t="s">
         <v>294</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>46316.659392928239</v>
       </c>
     </row>
-    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" t="s">
         <v>295</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>46316.659700798613</v>
       </c>
     </row>
-    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" t="s">
         <v>296</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>46316.660021215277</v>
       </c>
     </row>
-    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" t="s">
         <v>298</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>46316.663523344905</v>
       </c>
     </row>
-    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" t="s">
         <v>299</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>46316.66397306713</v>
       </c>
     </row>
-    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" t="s">
         <v>300</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>46316.655218993059</v>
       </c>
     </row>
-    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" t="s">
         <v>301</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>46316.66474547454</v>
       </c>
     </row>
-    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" t="s">
         <v>303</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>46316.665075289355</v>
       </c>
     </row>
-    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" t="s">
         <v>304</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>46316.665315798607</v>
       </c>
     </row>
-    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" t="s">
         <v>305</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>46316.665554606479</v>
       </c>
     </row>
-    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" t="s">
         <v>306</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>46316.666150277779</v>
       </c>
     </row>
-    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" t="s">
         <v>307</v>
       </c>
@@ -4574,10 +4574,10 @@
         <v>46316.66728306713</v>
       </c>
       <c r="D320" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" t="s">
         <v>309</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>46316.667589375</v>
       </c>
     </row>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" t="s">
         <v>310</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>46317.34018446759</v>
       </c>
     </row>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" t="s">
         <v>312</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>46317.350805567126</v>
       </c>
     </row>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" t="s">
         <v>313</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>46317.350040347221</v>
       </c>
     </row>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" t="s">
         <v>314</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>46317.349033449071</v>
       </c>
     </row>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" t="s">
         <v>315</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>46317.348020972226</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" t="s">
         <v>317</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>46317.348241458334</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" t="s">
         <v>318</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>46317.347743738428</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" t="s">
         <v>319</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>46317.350477280095</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" t="s">
         <v>320</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>46317.347308449076</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" t="s">
         <v>321</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>46317.345922685185</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" t="s">
         <v>322</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>46317.346541550927</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" t="s">
         <v>324</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>46317.345109942129</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" t="s">
         <v>326</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>46317.346153784725</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" t="s">
         <v>327</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>46317.344782118053</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" t="s">
         <v>328</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>46317.344479212959</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" t="s">
         <v>329</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>46317.343963506944</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" t="s">
         <v>330</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>46317.345313055557</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" t="s">
         <v>331</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>46317.344191875003</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" t="s">
         <v>332</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>46317.346821921295</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" t="s">
         <v>333</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>46317.349823645833</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" t="s">
         <v>334</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>46317.351432847223</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" t="s">
         <v>335</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>46317.363271354166</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" t="s">
         <v>340</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>46317.368958587962</v>
       </c>
     </row>
-    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" t="s">
         <v>341</v>
       </c>
@@ -4870,10 +4870,10 @@
         <v>46317.391570717591</v>
       </c>
       <c r="D354" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" t="s">
         <v>343</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>46317.391111435187</v>
       </c>
     </row>
-    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" t="s">
         <v>344</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>46317.398353379627</v>
       </c>
     </row>
-    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" t="s">
         <v>345</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>46317.41721107639</v>
       </c>
     </row>
-    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" t="s">
         <v>346</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>46317.406281446762</v>
       </c>
     </row>
-    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" t="s">
         <v>347</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>46317.415765983795</v>
       </c>
     </row>
-    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" t="s">
         <v>348</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>46317.416297141201</v>
       </c>
     </row>
-    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" t="s">
         <v>349</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>46317.417663981483</v>
       </c>
     </row>
-    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" t="s">
         <v>351</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>46317.419560358794</v>
       </c>
     </row>
-    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" t="s">
         <v>352</v>
       </c>
@@ -4961,13 +4961,13 @@
         <v>326</v>
       </c>
       <c r="B365" t="s">
-        <v>421</v>
+        <v>494</v>
       </c>
       <c r="C365" s="1">
         <v>46317.429868819447</v>
       </c>
     </row>
-    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" t="s">
         <v>328</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>46317.430422754631</v>
       </c>
     </row>
-    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" t="s">
         <v>353</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>46317.444625289354</v>
       </c>
       <c r="D368" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -5002,13 +5002,13 @@
         <v>355</v>
       </c>
       <c r="B369" t="s">
-        <v>422</v>
+        <v>494</v>
       </c>
       <c r="C369" s="1">
         <v>46317.445218726854</v>
       </c>
     </row>
-    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" t="s">
         <v>356</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>46317.449088368056</v>
       </c>
     </row>
-    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" t="s">
         <v>359</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>46317.448752662036</v>
       </c>
     </row>
-    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" t="s">
         <v>360</v>
       </c>
@@ -5059,13 +5059,13 @@
         <v>361</v>
       </c>
       <c r="B375" t="s">
-        <v>423</v>
+        <v>494</v>
       </c>
       <c r="C375" s="1">
         <v>46317.45133329861</v>
       </c>
     </row>
-    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" t="s">
         <v>362</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>46317.451688761575</v>
       </c>
     </row>
-    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" t="s">
         <v>363</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>46317.465697962965</v>
       </c>
     </row>
-    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" t="s">
         <v>365</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>46317.466039166669</v>
       </c>
     </row>
-    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" t="s">
         <v>366</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>46317.46762891204</v>
       </c>
     </row>
-    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" t="s">
         <v>368</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>46317.467955578701</v>
       </c>
     </row>
-    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" t="s">
         <v>369</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>46317.475458680557</v>
       </c>
     </row>
-    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" t="s">
         <v>371</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>46317.47680895833</v>
       </c>
     </row>
-    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" t="s">
         <v>372</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>46317.484748391202</v>
       </c>
     </row>
-    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" t="s">
         <v>374</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>46317.485875254628</v>
       </c>
     </row>
-    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" t="s">
         <v>376</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>46317.486205717592</v>
       </c>
     </row>
-    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" t="s">
         <v>377</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>46317.48728079861</v>
       </c>
     </row>
-    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" t="s">
         <v>378</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>46317.487546087963</v>
       </c>
     </row>
-    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" t="s">
         <v>379</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>46317.508724675929</v>
       </c>
     </row>
-    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" t="s">
         <v>380</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>46317.508313055558</v>
       </c>
     </row>
-    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" t="s">
         <v>381</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>46317.524752314814</v>
       </c>
     </row>
-    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" t="s">
         <v>383</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>46317.559528425925</v>
       </c>
     </row>
-    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" t="s">
         <v>384</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>46317.559787638886</v>
       </c>
     </row>
-    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" t="s">
         <v>385</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>46317.561094143515</v>
       </c>
     </row>
-    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" t="s">
         <v>386</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>46317.566485555559</v>
       </c>
     </row>
-    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" t="s">
         <v>388</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>46317.581182627313</v>
       </c>
     </row>
-    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" t="s">
         <v>390</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>46317.590580694443</v>
       </c>
     </row>
-    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" t="s">
         <v>391</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>46317.589558506945</v>
       </c>
     </row>
-    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" t="s">
         <v>392</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>46317.589234270832</v>
       </c>
     </row>
-    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" t="s">
         <v>393</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>46317.589938356483</v>
       </c>
     </row>
-    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" t="s">
         <v>394</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>46317.59126212963</v>
       </c>
     </row>
-    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" t="s">
         <v>395</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>46317.610700567129</v>
       </c>
     </row>
-    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" t="s">
         <v>396</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>46317.610324675923</v>
       </c>
     </row>
-    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" t="s">
         <v>397</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>46317.612850925929</v>
       </c>
     </row>
-    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" t="s">
         <v>398</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>46317.640879293984</v>
       </c>
     </row>
-    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" t="s">
         <v>399</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>46317.641344768519</v>
       </c>
     </row>
-    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" t="s">
         <v>400</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>46317.654907002317</v>
       </c>
     </row>
-    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" t="s">
         <v>402</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>46317.654567361111</v>
       </c>
     </row>
-    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" t="s">
         <v>403</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>46317.655494780091</v>
       </c>
     </row>
-    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" t="s">
         <v>328</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>46317.665912233795</v>
       </c>
     </row>
-    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" t="s">
         <v>404</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>46317.669549907405</v>
       </c>
     </row>
-    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" t="s">
         <v>405</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>46317.673811365741</v>
       </c>
     </row>
-    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" t="s">
         <v>406</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>46317.675059965281</v>
       </c>
     </row>
-    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" t="s">
         <v>407</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>46317.678380057871</v>
       </c>
     </row>
-    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" t="s">
         <v>408</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>46317.688480925928</v>
       </c>
     </row>
-    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" t="s">
         <v>409</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>46317.688784965278</v>
       </c>
     </row>
-    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" t="s">
         <v>410</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>46317.70125471065</v>
       </c>
     </row>
-    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" t="s">
         <v>413</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>46317.701605613423</v>
       </c>
     </row>
-    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" t="s">
         <v>414</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>46317.702259745369</v>
       </c>
     </row>
-    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" t="s">
         <v>328</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>46318.189411504631</v>
       </c>
     </row>
-    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" t="s">
         <v>415</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>46317.713062199073</v>
       </c>
     </row>
-    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" t="s">
         <v>416</v>
       </c>
@@ -5554,17 +5554,17 @@
         <v>46317.720143217593</v>
       </c>
     </row>
-    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C433" s="1">
         <v>46318.379348645831</v>
       </c>
     </row>
-    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C434" s="1">
         <v>46318.381625682872</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B435" t="s">
         <v>5</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B436" t="s">
         <v>418</v>
@@ -5592,17 +5592,17 @@
         <v>46318.380657002315</v>
       </c>
     </row>
-    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C437" s="1">
         <v>46318.389500694444</v>
       </c>
     </row>
-    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C438" s="1">
         <v>46318.390437037036</v>
@@ -5610,18 +5610,18 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B439" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C439" s="1">
         <v>46318.3907421412</v>
       </c>
     </row>
-    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C440" s="1">
         <v>46318.382043310186</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B441" t="s">
         <v>5</v>
@@ -5638,9 +5638,9 @@
         <v>46318.382311851848</v>
       </c>
     </row>
-    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C442" s="1">
         <v>46318.388368819447</v>
@@ -5648,66 +5648,66 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B443" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C443" s="1">
         <v>46318.391407442126</v>
       </c>
     </row>
-    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C444" s="1">
         <v>46318.39166090278</v>
       </c>
     </row>
-    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C445" s="1">
         <v>46318.392170902778</v>
       </c>
     </row>
-    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A446" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C446" s="1">
         <v>46318.392382523147</v>
       </c>
     </row>
-    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A447" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C447" s="1">
         <v>46318.393054537039</v>
       </c>
     </row>
-    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C448" s="1">
         <v>46318.393303541663</v>
       </c>
     </row>
-    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A449" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C449" s="1">
         <v>46318.393715428239</v>
       </c>
     </row>
-    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A450" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C450" s="1">
         <v>46318.393936250002</v>
@@ -5715,7 +5715,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A451" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B451" t="s">
         <v>4</v>
@@ -5724,9 +5724,9 @@
         <v>46318.405059398145</v>
       </c>
     </row>
-    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A452" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C452" s="1">
         <v>46318.405408715276</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B453" t="s">
         <v>4</v>
@@ -5743,49 +5743,49 @@
         <v>46318.40583358796</v>
       </c>
     </row>
-    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A454" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C454" s="1">
         <v>46318.427280868054</v>
       </c>
     </row>
-    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A455" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C455" s="1">
         <v>46318.427044699078</v>
       </c>
     </row>
-    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A456" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C456" s="1">
         <v>46318.426807314812</v>
       </c>
     </row>
-    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A457" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C457" s="1">
         <v>46318.427580231481</v>
       </c>
     </row>
-    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A458" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C458" s="1">
         <v>46318.427793194445</v>
       </c>
     </row>
-    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A459" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C459" s="1">
         <v>46318.432990428242</v>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A460" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B460" t="s">
         <v>5</v>
@@ -5802,12 +5802,12 @@
         <v>46318.433417129629</v>
       </c>
       <c r="D460" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A461" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B461" t="s">
         <v>5</v>
@@ -5816,65 +5816,65 @@
         <v>46318.439424571756</v>
       </c>
     </row>
-    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C462" s="1">
         <v>46318.443270636577</v>
       </c>
     </row>
-    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A463" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C463" s="1">
         <v>46318.490852650466</v>
       </c>
     </row>
-    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C464" s="1">
         <v>46318.491102314816</v>
       </c>
     </row>
-    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C465" s="1">
         <v>46318.490891666668</v>
       </c>
     </row>
-    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A466" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C466" s="1">
         <v>46318.490296215277</v>
       </c>
     </row>
-    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A467" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C467" s="1">
         <v>46318.491128368056</v>
       </c>
     </row>
-    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A468" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C468" s="1">
         <v>46318.491340925924</v>
       </c>
     </row>
-    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A469" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C469" s="1">
         <v>46318.492865347223</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A470" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B470" t="s">
         <v>5</v>
@@ -5891,68 +5891,68 @@
         <v>46318.491616828702</v>
       </c>
       <c r="D470" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A471" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C471" s="1">
         <v>46318.494003402775</v>
       </c>
     </row>
-    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A472" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C472" s="1">
         <v>46318.493984884262</v>
       </c>
     </row>
-    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A473" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C473" s="1">
         <v>46318.503831469905</v>
       </c>
     </row>
-    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A474" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C474" s="1">
         <v>46318.504232881947</v>
       </c>
     </row>
-    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A475" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C475" s="1">
         <v>46318.52962050926</v>
       </c>
     </row>
-    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A476" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C476" s="1">
         <v>46318.530970740743</v>
       </c>
     </row>
-    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A477" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C477" s="1">
         <v>46318.565858321759</v>
       </c>
     </row>
-    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A478" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C478" s="1">
         <v>46318.575484629633</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B479" t="s">
         <v>4</v>
@@ -5969,9 +5969,9 @@
         <v>46318.583952372683</v>
       </c>
     </row>
-    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A480" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C480" s="1">
         <v>46318.584380127315</v>
@@ -5979,7 +5979,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A481" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B481" t="s">
         <v>4</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A482" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B482" t="s">
         <v>5</v>
@@ -5999,12 +5999,12 @@
         <v>46318.614888750002</v>
       </c>
       <c r="D482" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A483" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B483" t="s">
         <v>5</v>
@@ -6013,17 +6013,17 @@
         <v>46318.614326608797</v>
       </c>
     </row>
-    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A484" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C484" s="1">
         <v>46318.614601331021</v>
       </c>
     </row>
-    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A485" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C485" s="1">
         <v>46318.614003946757</v>
@@ -6031,7 +6031,7 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A486" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B486" t="s">
         <v>5</v>
@@ -6040,94 +6040,88 @@
         <v>46318.615288530091</v>
       </c>
     </row>
-    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C487" s="1">
         <v>46318.615708101854</v>
       </c>
     </row>
-    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A488" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C488" s="1">
         <v>46318.620106828705</v>
       </c>
     </row>
-    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A489" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C489" s="1">
         <v>46318.623910833332</v>
       </c>
     </row>
-    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A490" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C490" s="1">
         <v>46318.626468298608</v>
       </c>
     </row>
-    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A491" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C491" s="1">
         <v>46318.635854305554</v>
       </c>
     </row>
-    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A492" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C492" s="1">
         <v>46318.636147372687</v>
       </c>
     </row>
-    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A493" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C493" s="1">
         <v>46318.636435879627</v>
       </c>
     </row>
-    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A494" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C494" s="1">
         <v>46318.646399155092</v>
       </c>
     </row>
-    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A495" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C495" s="1">
         <v>46318.64666421296</v>
       </c>
     </row>
-    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C496" s="1">
         <v>46318.651625798608</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D496" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D496" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
